--- a/data/P2/P2T1_BQ2.xlsx
+++ b/data/P2/P2T1_BQ2.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/P2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{908222AB-8A3B-374C-89FD-7636AA0A0FEE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08A5D9DC-C3E1-1E4E-AD29-655AFB72F098}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="460" windowWidth="24820" windowHeight="15020" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
+    <workbookView xWindow="31160" yWindow="4520" windowWidth="24820" windowHeight="15020" activeTab="1" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="工作表2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
   <si>
     <t>word</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -217,13 +218,63 @@
   </si>
   <si>
     <t>美味</t>
+  </si>
+  <si>
+    <t>We can see and feel solids. Some solids are hard, and some solids are soft.</t>
+  </si>
+  <si>
+    <t>我們可以看見和觸摸到固體。有些固體很硬，有些固體很柔軟。</t>
+  </si>
+  <si>
+    <t>When we make water very cold, it freezes and changes to ice.</t>
+  </si>
+  <si>
+    <t>當我們把水變得非常冷，它會結冰並變成冰。</t>
+  </si>
+  <si>
+    <t>A liquid is a thing that can flow. Some liquids are thick, and some liquids are thin.</t>
+  </si>
+  <si>
+    <t>液體是會流動的東西。有些液體很濃稠，有些液體很稀薄。</t>
+  </si>
+  <si>
+    <t>When ice or snow heats up, it melts and changes back to water.</t>
+  </si>
+  <si>
+    <t>當冰或雪受熱，它會融化並變回水。</t>
+  </si>
+  <si>
+    <t>The air that you breathe is a gas.</t>
+  </si>
+  <si>
+    <t>你呼吸的空氣是一種氣體。</t>
+  </si>
+  <si>
+    <t>We can’t usually see a gas, but sometimes we can feel it when it moves.</t>
+  </si>
+  <si>
+    <t>我們通常看不見氣體，但有時當它流動時我們可以感覺到。</t>
+  </si>
+  <si>
+    <t>When we heat water, it boils and changes to steam.</t>
+  </si>
+  <si>
+    <t>當我們加熱水，它會沸騰並變成水蒸氣。</t>
+  </si>
+  <si>
+    <t>sentence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chinese</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -244,6 +295,15 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -268,11 +328,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -937,4 +1000,82 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E4653B0-B8A7-AE4E-821B-58E6E96A831D}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="71.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/P2/P2T1_BQ2.xlsx
+++ b/data/P2/P2T1_BQ2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/P2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08A5D9DC-C3E1-1E4E-AD29-655AFB72F098}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ECDC468-4EB3-A846-8588-A18378223074}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31160" yWindow="4520" windowWidth="24820" windowHeight="15020" activeTab="1" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
+    <workbookView xWindow="31160" yWindow="4520" windowWidth="24820" windowHeight="15020" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="132">
   <si>
     <t>word</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -267,6 +267,167 @@
   </si>
   <si>
     <t>chinese</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/ˈsɒlɪd/</t>
+  </si>
+  <si>
+    <t>sol-id</t>
+  </si>
+  <si>
+    <t>/ˈlɪkwɪd/</t>
+  </si>
+  <si>
+    <t>liq-uid</t>
+  </si>
+  <si>
+    <t>/ɡæs/</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t>/fləʊ/</t>
+  </si>
+  <si>
+    <t>/hiːt/</t>
+  </si>
+  <si>
+    <t>/stiːm/</t>
+  </si>
+  <si>
+    <t>/friːz/</t>
+  </si>
+  <si>
+    <t>/melt/</t>
+  </si>
+  <si>
+    <t>/ˈketl/</t>
+  </si>
+  <si>
+    <t>ket-tle</t>
+  </si>
+  <si>
+    <t>/ˈfriːzə(r)/</t>
+  </si>
+  <si>
+    <t>freez-er</t>
+  </si>
+  <si>
+    <t>/aɪs ˈkjuːbz/</t>
+  </si>
+  <si>
+    <t>ice-cubes</t>
+  </si>
+  <si>
+    <t>/fruːt/</t>
+  </si>
+  <si>
+    <t>/ˈvedʒtəblz/</t>
+  </si>
+  <si>
+    <t>veg-e-ta-bles</t>
+  </si>
+  <si>
+    <t>/ˈsæləd/</t>
+  </si>
+  <si>
+    <t>sal-ad</t>
+  </si>
+  <si>
+    <t>/ˈkjuːkʌmbəz/</t>
+  </si>
+  <si>
+    <t>cu-cum-bers</t>
+  </si>
+  <si>
+    <t>/ˌævəˈkɑːdəʊz/</t>
+  </si>
+  <si>
+    <t>av-o-ca-dos</t>
+  </si>
+  <si>
+    <t>/ˈletɪs/</t>
+  </si>
+  <si>
+    <t>let-tuce</t>
+  </si>
+  <si>
+    <t>/ˈsɒsɪdʒɪz/</t>
+  </si>
+  <si>
+    <t>sau-sa-ges</t>
+  </si>
+  <si>
+    <t>/ˈsænwɪdʒɪz/</t>
+  </si>
+  <si>
+    <t>sand-wich-es</t>
+  </si>
+  <si>
+    <t>/ˈpæstə/</t>
+  </si>
+  <si>
+    <t>pas-ta</t>
+  </si>
+  <si>
+    <t>/ˈpænkeɪks/</t>
+  </si>
+  <si>
+    <t>pan-cakes</t>
+  </si>
+  <si>
+    <t>/ˈflaʊə(r)/</t>
+  </si>
+  <si>
+    <t>/ˈbʌtə(r)/</t>
+  </si>
+  <si>
+    <t>but-ter</t>
+  </si>
+  <si>
+    <t>/ˈmeɪpl ˈsɪrəp/</t>
+  </si>
+  <si>
+    <t>ma-ple sy-rup</t>
+  </si>
+  <si>
+    <t>/pɔː(r)/</t>
+  </si>
+  <si>
+    <t>/mɪks/</t>
+  </si>
+  <si>
+    <t>/flɪp ˈəʊvə(r)/</t>
+  </si>
+  <si>
+    <t>flip o-ver</t>
+  </si>
+  <si>
+    <t>/ˈmɪkstʃə(r)/</t>
+  </si>
+  <si>
+    <t>mix-ture</t>
+  </si>
+  <si>
+    <t>/ˈfraɪɪŋ pæn/</t>
+  </si>
+  <si>
+    <t>fry-ing pan</t>
+  </si>
+  <si>
+    <t>/dɪˈlɪʃəs/</t>
+  </si>
+  <si>
+    <t>de-li-cious</t>
+  </si>
+  <si>
+    <t>phonetics</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>syllable</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -652,10 +813,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{527ABE91-7216-BA4F-A91C-2F06E544A41C}">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="3" width="4.83203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -665,8 +829,17 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -676,8 +849,14 @@
       <c r="C2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="D2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -687,8 +866,14 @@
       <c r="C3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="D3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -698,8 +883,14 @@
       <c r="C4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -709,8 +900,14 @@
       <c r="C5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="D5" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -720,8 +917,14 @@
       <c r="C6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="D6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -731,8 +934,14 @@
       <c r="C7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
@@ -742,8 +951,14 @@
       <c r="C8">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -753,8 +968,14 @@
       <c r="C9">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="D9" t="s">
+        <v>89</v>
+      </c>
+      <c r="E9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -764,8 +985,14 @@
       <c r="C10">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
+      <c r="D10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
@@ -775,8 +1002,14 @@
       <c r="C11">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="D11" t="s">
+        <v>92</v>
+      </c>
+      <c r="E11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
@@ -786,8 +1019,14 @@
       <c r="C12">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
+      <c r="D12" t="s">
+        <v>94</v>
+      </c>
+      <c r="E12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
@@ -797,8 +1036,14 @@
       <c r="C13">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
+      <c r="D13" t="s">
+        <v>96</v>
+      </c>
+      <c r="E13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
@@ -808,8 +1053,14 @@
       <c r="C14">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:3">
+      <c r="D14" t="s">
+        <v>97</v>
+      </c>
+      <c r="E14" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
@@ -819,8 +1070,14 @@
       <c r="C15">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
+      <c r="D15" t="s">
+        <v>99</v>
+      </c>
+      <c r="E15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
@@ -830,8 +1087,14 @@
       <c r="C16">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16" t="s">
+        <v>101</v>
+      </c>
+      <c r="E16" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
         <v>18</v>
       </c>
@@ -841,8 +1104,14 @@
       <c r="C17">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="D17" t="s">
+        <v>103</v>
+      </c>
+      <c r="E17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
@@ -852,8 +1121,14 @@
       <c r="C18">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18" t="s">
+        <v>105</v>
+      </c>
+      <c r="E18" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
         <v>20</v>
       </c>
@@ -863,8 +1138,14 @@
       <c r="C19">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19" t="s">
+        <v>107</v>
+      </c>
+      <c r="E19" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="1" t="s">
         <v>21</v>
       </c>
@@ -874,8 +1155,14 @@
       <c r="C20">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="D20" t="s">
+        <v>109</v>
+      </c>
+      <c r="E20" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="1" t="s">
         <v>22</v>
       </c>
@@ -885,8 +1172,14 @@
       <c r="C21">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
+      <c r="D21" t="s">
+        <v>111</v>
+      </c>
+      <c r="E21" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="1" t="s">
         <v>23</v>
       </c>
@@ -896,8 +1189,14 @@
       <c r="C22">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
+      <c r="D22" t="s">
+        <v>113</v>
+      </c>
+      <c r="E22" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" s="1" t="s">
         <v>24</v>
       </c>
@@ -907,8 +1206,14 @@
       <c r="C23">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
+      <c r="D23" t="s">
+        <v>115</v>
+      </c>
+      <c r="E23" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" s="1" t="s">
         <v>25</v>
       </c>
@@ -918,8 +1223,14 @@
       <c r="C24">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
+      <c r="D24" t="s">
+        <v>116</v>
+      </c>
+      <c r="E24" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" s="1" t="s">
         <v>26</v>
       </c>
@@ -929,8 +1240,14 @@
       <c r="C25">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
+      <c r="D25" t="s">
+        <v>118</v>
+      </c>
+      <c r="E25" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" s="1" t="s">
         <v>27</v>
       </c>
@@ -940,8 +1257,14 @@
       <c r="C26">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
+      <c r="D26" t="s">
+        <v>120</v>
+      </c>
+      <c r="E26" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" s="1" t="s">
         <v>28</v>
       </c>
@@ -951,8 +1274,14 @@
       <c r="C27">
         <v>6</v>
       </c>
-    </row>
-    <row r="28" spans="1:3">
+      <c r="D27" t="s">
+        <v>121</v>
+      </c>
+      <c r="E27" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" s="1" t="s">
         <v>29</v>
       </c>
@@ -962,8 +1291,14 @@
       <c r="C28">
         <v>6</v>
       </c>
-    </row>
-    <row r="29" spans="1:3">
+      <c r="D28" t="s">
+        <v>122</v>
+      </c>
+      <c r="E28" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" s="1" t="s">
         <v>30</v>
       </c>
@@ -973,8 +1308,14 @@
       <c r="C29">
         <v>6</v>
       </c>
-    </row>
-    <row r="30" spans="1:3">
+      <c r="D29" t="s">
+        <v>124</v>
+      </c>
+      <c r="E29" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" s="1" t="s">
         <v>31</v>
       </c>
@@ -984,8 +1325,14 @@
       <c r="C30">
         <v>6</v>
       </c>
-    </row>
-    <row r="31" spans="1:3">
+      <c r="D30" t="s">
+        <v>126</v>
+      </c>
+      <c r="E30" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" s="1" t="s">
         <v>32</v>
       </c>
@@ -994,6 +1341,12 @@
       </c>
       <c r="C31">
         <v>6</v>
+      </c>
+      <c r="D31" t="s">
+        <v>128</v>
+      </c>
+      <c r="E31" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/data/P2/P2T1_BQ2.xlsx
+++ b/data/P2/P2T1_BQ2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/data/P2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/homes/ximonlam/Mac/單詞複習網素材/English/data/P2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ECDC468-4EB3-A846-8588-A18378223074}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1738D09C-8A05-3F42-9DEC-383ACED833AC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31160" yWindow="4520" windowWidth="24820" windowHeight="15020" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
+    <workbookView xWindow="34360" yWindow="460" windowWidth="26560" windowHeight="20480" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="163">
   <si>
     <t>word</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -429,6 +429,100 @@
   <si>
     <t>syllable</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>English explanation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Matter with hard shape, it does not change form easily</t>
+  </si>
+  <si>
+    <t>Wet matter that can flow and take the shape of its cup</t>
+  </si>
+  <si>
+    <t>Light invisible matter that spreads out everywhere</t>
+  </si>
+  <si>
+    <t>Move slowly like water moving down</t>
+  </si>
+  <si>
+    <t>Warm or hot energy that can change things</t>
+  </si>
+  <si>
+    <t>Hot white gas from boiling hot water</t>
+  </si>
+  <si>
+    <t>Turn liquid water into hard ice when very cold</t>
+  </si>
+  <si>
+    <t>Turn solid ice into water when warm</t>
+  </si>
+  <si>
+    <t>A pot used to boil hot water</t>
+  </si>
+  <si>
+    <t>Cold box that makes water turn into ice</t>
+  </si>
+  <si>
+    <t>Small hard square blocks of frozen water</t>
+  </si>
+  <si>
+    <t>Sweet plant food like apples, bananas</t>
+  </si>
+  <si>
+    <t>Healthy green or fresh food from plants</t>
+  </si>
+  <si>
+    <t>Cold food mixed with many raw vegetables</t>
+  </si>
+  <si>
+    <t>Long green vegetable with smooth skin</t>
+  </si>
+  <si>
+    <t>Soft green fruit with one big hard seed inside</t>
+  </si>
+  <si>
+    <t>Soft green leaf vegetable for salads</t>
+  </si>
+  <si>
+    <t>Long thin meat food</t>
+  </si>
+  <si>
+    <t>Two pieces of bread with food inside</t>
+  </si>
+  <si>
+    <t>Soft noodle food made from flour</t>
+  </si>
+  <si>
+    <t>Thin flat round cakes cooked in a pan</t>
+  </si>
+  <si>
+    <t>Soft white powder to make bread and cakes</t>
+  </si>
+  <si>
+    <t>Soft yellow creamy food from milk</t>
+  </si>
+  <si>
+    <t>Sweet brown thick liquid for pancakes</t>
+  </si>
+  <si>
+    <t>Let liquid flow out from a cup or bottle</t>
+  </si>
+  <si>
+    <t>Put different foods together and stir</t>
+  </si>
+  <si>
+    <t>Turn food to cook its other side</t>
+  </si>
+  <si>
+    <t>Many different things mixed together</t>
+  </si>
+  <si>
+    <t>Flat metal pan for cooking food on fire</t>
+  </si>
+  <si>
+    <t>Food that tastes very good</t>
   </si>
 </sst>
 </file>
@@ -813,13 +907,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{527ABE91-7216-BA4F-A91C-2F06E544A41C}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="4.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -835,11 +929,14 @@
       <c r="E1" t="s">
         <v>131</v>
       </c>
-      <c r="F1" s="2"/>
+      <c r="F1" t="s">
+        <v>132</v>
+      </c>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -855,8 +952,11 @@
       <c r="E2" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="F2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -872,8 +972,11 @@
       <c r="E3" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="F3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -889,8 +992,11 @@
       <c r="E4" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="F4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -906,8 +1012,11 @@
       <c r="E5" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="F5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -923,8 +1032,11 @@
       <c r="E6" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="F6" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -940,8 +1052,11 @@
       <c r="E7" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="F7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
@@ -957,8 +1072,11 @@
       <c r="E8" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="F8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -974,8 +1092,11 @@
       <c r="E9" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="F9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -991,8 +1112,11 @@
       <c r="E10" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="F10" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
@@ -1008,8 +1132,11 @@
       <c r="E11" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="F11" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
@@ -1025,8 +1152,11 @@
       <c r="E12" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="F12" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
@@ -1042,8 +1172,11 @@
       <c r="E13" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="F13" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
@@ -1059,8 +1192,11 @@
       <c r="E14" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="F14" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
@@ -1076,8 +1212,11 @@
       <c r="E15" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="F15" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
@@ -1093,8 +1232,11 @@
       <c r="E16" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
         <v>18</v>
       </c>
@@ -1110,8 +1252,11 @@
       <c r="E17" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
@@ -1127,8 +1272,11 @@
       <c r="E18" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="1" t="s">
         <v>20</v>
       </c>
@@ -1144,8 +1292,11 @@
       <c r="E19" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="F19" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="1" t="s">
         <v>21</v>
       </c>
@@ -1161,8 +1312,11 @@
       <c r="E20" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="F20" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
         <v>22</v>
       </c>
@@ -1178,8 +1332,11 @@
       <c r="E21" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="F21" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" s="1" t="s">
         <v>23</v>
       </c>
@@ -1195,8 +1352,11 @@
       <c r="E22" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="F22" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" s="1" t="s">
         <v>24</v>
       </c>
@@ -1212,8 +1372,11 @@
       <c r="E23" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="F23" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" s="1" t="s">
         <v>25</v>
       </c>
@@ -1229,8 +1392,11 @@
       <c r="E24" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="F24" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" s="1" t="s">
         <v>26</v>
       </c>
@@ -1246,8 +1412,11 @@
       <c r="E25" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="F25" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" s="1" t="s">
         <v>27</v>
       </c>
@@ -1263,8 +1432,11 @@
       <c r="E26" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="27" spans="1:5">
+      <c r="F26" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" s="1" t="s">
         <v>28</v>
       </c>
@@ -1280,8 +1452,11 @@
       <c r="E27" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="28" spans="1:5">
+      <c r="F27" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" s="1" t="s">
         <v>29</v>
       </c>
@@ -1297,8 +1472,11 @@
       <c r="E28" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="29" spans="1:5">
+      <c r="F28" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29" s="1" t="s">
         <v>30</v>
       </c>
@@ -1314,8 +1492,11 @@
       <c r="E29" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="30" spans="1:5">
+      <c r="F29" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30" s="1" t="s">
         <v>31</v>
       </c>
@@ -1331,8 +1512,11 @@
       <c r="E30" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="31" spans="1:5">
+      <c r="F30" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31" s="1" t="s">
         <v>32</v>
       </c>
@@ -1347,6 +1531,9 @@
       </c>
       <c r="E31" t="s">
         <v>129</v>
+      </c>
+      <c r="F31" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>
